--- a/dotnet/tests/corpus/features/sheet-small-band-xlsx.xlsx
+++ b/dotnet/tests/corpus/features/sheet-small-band-xlsx.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Zero" sheetId="2" r:id="rId2"/>
     <sheet name="Roomy" sheetId="3" r:id="rId3"/>
     <sheet name="Snug" sheetId="4" r:id="rId5"/>
+    <sheet name="Spill" sheetId="5" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -119,4 +120,26 @@
     <oddFooter>&amp;CSNUGBAND</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SpillBody</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.3" header="0.5" footer="0.25"/>
+  <pageSetup orientation="portrait"/>
+  <headerFooter>
+    <oddFooter>&amp;R&amp;9SPILLONE
+&amp;9SPILLTWO
+&amp;9SPILLTHREE</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>